--- a/artfynd/A 22783-2025 artfynd.xlsx
+++ b/artfynd/A 22783-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118633315</v>
+        <v>119809437</v>
       </c>
       <c r="B2" t="n">
-        <v>57403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sakris-Pettersbodarna (Sakris-Pettersbodarna), Ång</t>
+          <t>Ö om Gårdsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583896</v>
+        <v>583529</v>
       </c>
       <c r="R2" t="n">
-        <v>7026601</v>
+        <v>7027171</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På grov, gammal sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,65 +765,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Camilla Pakka</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Camilla Pakka</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119809436</v>
+        <v>133126949</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ö om Gårdsjöbäcken, Ång</t>
+          <t>Edsele, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583529</v>
+        <v>583574</v>
       </c>
       <c r="R3" t="n">
-        <v>7027171</v>
+        <v>7026858</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,17 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På grov, gammal sälg.</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Emmy Ransgart</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Via Emmy Ransgart</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -901,12 +877,7 @@
         <v>119809438</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119809437</v>
+        <v>131042364</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,37 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ö om Gårdsjöbäcken, Ång</t>
+          <t>Sakris-Pettersbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583529</v>
+        <v>583967</v>
       </c>
       <c r="R5" t="n">
-        <v>7027171</v>
+        <v>7026635</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,17 +1041,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov, gammal sälg.</t>
+          <t>Observationen är gjord i samband med fågelinventeringar i SvK:s projekt Inlandspaktet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,65 +1076,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Martin Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Martin Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119809435</v>
+        <v>133126948</v>
       </c>
       <c r="B6" t="n">
-        <v>79658</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ö om Gårdsjöbäcken, Ång</t>
+          <t>Edsele, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583528</v>
+        <v>583602</v>
       </c>
       <c r="R6" t="n">
-        <v>7027172</v>
+        <v>7026872</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov, gammal sälg.</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,27 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Emmy Ransgart</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Via Emmy Ransgart</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121463444</v>
+        <v>119809436</v>
       </c>
       <c r="B7" t="n">
-        <v>56258</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,48 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205992</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Edsele, Ång</t>
+          <t>Ö om Gårdsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583905</v>
+        <v>583529</v>
       </c>
       <c r="R7" t="n">
-        <v>7026606</v>
+        <v>7027171</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,12 +1250,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På grov, gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,76 +1275,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lindy Sörman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lindy Sörman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121463446</v>
+        <v>119809435</v>
       </c>
       <c r="B8" t="n">
-        <v>56251</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Edsele, Ång</t>
+          <t>Ö om Gårdsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583905</v>
+        <v>583528</v>
       </c>
       <c r="R8" t="n">
-        <v>7026606</v>
+        <v>7027172</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,12 +1352,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På grov, gammal sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lindy Sörman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lindy Sörman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133126948</v>
+        <v>118633315</v>
       </c>
       <c r="B9" t="n">
-        <v>80439</v>
+        <v>58057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,37 +1400,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Edsele, Ång</t>
+          <t>Sakris-Pettersbodarna, Sakris-Pettersbodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583602</v>
+        <v>583896</v>
       </c>
       <c r="R9" t="n">
-        <v>7026872</v>
+        <v>7026601</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,12 +1458,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,60 +1488,74 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emmy Ransgart</t>
+          <t>Camilla Pakka</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Emmy Ransgart</t>
+          <t>Camilla Pakka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133126949</v>
+        <v>121463444</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>56823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>205992</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edsele, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583574</v>
+        <v>583905</v>
       </c>
       <c r="R10" t="n">
-        <v>7026858</v>
+        <v>7026606</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,12 +1579,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,15 +1599,126 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emmy Ransgart</t>
+          <t>Lindy Sörman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Emmy Ransgart</t>
+          <t>Lindy Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121463446</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Edsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>583905</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7026606</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lindy Sörman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lindy Sörman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22783-2025 artfynd.xlsx
+++ b/artfynd/A 22783-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809437</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133126949</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809438</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131042364</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133126948</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809436</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809435</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118633315</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121463444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121463446</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,8 +1872,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131884797</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>